--- a/population-projection/src/main/resources/population_data/Biraben-USSR.xlsx
+++ b/population-projection/src/main/resources/population_data/Biraben-USSR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\population_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB39DE0-144C-427A-83FD-F2C0C5F19F5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33C1908-BA2F-4947-AC66-D94C056BD916}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="3" xr2:uid="{1C2A8E74-6A01-4ECA-AF22-4D7875460B7A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
   <si>
     <t>год</t>
   </si>
@@ -212,6 +212,12 @@
   <si>
     <t>— на данных о выживших, указанных в переписях населения, и оценках показателей выживаемости, основанных на ежегодных событиях с 1931 по 1934 год и с 1941 по 1949 год.</t>
   </si>
+  <si>
+    <t>т.к. они были эвакуированы.</t>
+  </si>
+  <si>
+    <t>Оцениваемое население не включает не включает прежнее (до 1945 года) немецкое население Калининградской области и японское население Сахалина и Курил,</t>
+  </si>
 </sst>
 </file>
 
@@ -297,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -310,7 +316,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -322,6 +327,8 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4585,181 +4592,195 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4171DCF0-2ABE-4C89-BE7C-095D6FEF3DF5}">
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>35</v>
+      <c r="B27" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4777,51 +4798,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4829,7 +4850,7 @@
       <c r="A4">
         <v>1750</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>34000</v>
       </c>
       <c r="C4" s="1"/>
@@ -4839,7 +4860,7 @@
       <c r="A5">
         <v>1800</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>46000</v>
       </c>
       <c r="C5" s="1"/>
@@ -4849,7 +4870,7 @@
       <c r="A6">
         <v>1850</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>70000</v>
       </c>
       <c r="C6" s="1"/>
@@ -5112,16 +5133,16 @@
       <c r="B13" s="1">
         <v>82700</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>3740</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>3340</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>45.1</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>40.299999999999997</v>
       </c>
       <c r="I13" s="1">
@@ -7515,13 +7536,13 @@
       <c r="C61" s="1">
         <v>7050</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="11">
         <v>4180</v>
       </c>
       <c r="E61" s="2">
         <v>43.1</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61" s="12">
         <v>25.6</v>
       </c>
       <c r="G61" s="2">
@@ -7560,19 +7581,19 @@
       <c r="A62">
         <v>1915</v>
       </c>
-      <c r="B62" s="12">
+      <c r="B62" s="11">
         <v>164800</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="11">
         <v>6150</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="11">
         <v>7000</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E62" s="12">
         <v>37.4</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F62" s="12">
         <v>42.6</v>
       </c>
       <c r="I62" s="1">
@@ -7608,19 +7629,19 @@
       <c r="A63">
         <v>1916</v>
       </c>
-      <c r="B63" s="12">
+      <c r="B63" s="11">
         <v>163900</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="11">
         <v>5300</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="11">
         <v>6400</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E63" s="12">
         <v>32.5</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="12">
         <v>39.200000000000003</v>
       </c>
       <c r="I63" s="1">
@@ -7656,19 +7677,19 @@
       <c r="A64">
         <v>1917</v>
       </c>
-      <c r="B64" s="12">
+      <c r="B64" s="11">
         <v>162800</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="11">
         <v>4650</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="11">
         <v>7600</v>
       </c>
-      <c r="E64" s="13">
+      <c r="E64" s="12">
         <v>28.8</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="12">
         <v>47.1</v>
       </c>
       <c r="G64" s="2">
@@ -7707,19 +7728,19 @@
       <c r="A65">
         <v>1918</v>
       </c>
-      <c r="B65" s="12">
+      <c r="B65" s="11">
         <v>159600</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="11">
         <v>5100</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="11">
         <v>8500</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65" s="12">
         <v>32.4</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="12">
         <v>53.9</v>
       </c>
       <c r="G65" s="2">
@@ -7758,19 +7779,19 @@
       <c r="A66">
         <v>1919</v>
       </c>
-      <c r="B66" s="12">
+      <c r="B66" s="11">
         <v>156000</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="11">
         <v>4750</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="11">
         <v>6350</v>
       </c>
-      <c r="E66" s="13">
+      <c r="E66" s="12">
         <v>30.6</v>
       </c>
-      <c r="F66" s="13">
+      <c r="F66" s="12">
         <v>41</v>
       </c>
       <c r="G66" s="2">
@@ -7809,19 +7830,19 @@
       <c r="A67">
         <v>1920</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="11">
         <v>154400</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="11">
         <v>4870</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="11">
         <v>5700</v>
       </c>
-      <c r="E67" s="13">
+      <c r="E67" s="12">
         <v>31.7</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67" s="12">
         <v>37.1</v>
       </c>
       <c r="G67" s="2">
@@ -7860,19 +7881,19 @@
       <c r="A68">
         <v>1921</v>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="11">
         <v>153000</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="11">
         <v>5350</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="11">
         <v>4560</v>
       </c>
-      <c r="E68" s="13">
+      <c r="E68" s="12">
         <v>35</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68" s="12">
         <v>29.8</v>
       </c>
       <c r="G68" s="2">
@@ -7911,19 +7932,19 @@
       <c r="A69">
         <v>1922</v>
       </c>
-      <c r="B69" s="12">
+      <c r="B69" s="11">
         <v>153000</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="11">
         <v>5530</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="11">
         <v>5800</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="12">
         <v>36.200000000000003</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="12">
         <v>38</v>
       </c>
       <c r="G69" s="2">
@@ -7962,19 +7983,19 @@
       <c r="A70">
         <v>1923</v>
       </c>
-      <c r="B70" s="12">
+      <c r="B70" s="11">
         <v>152300</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="11">
         <v>6780</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="11">
         <v>3460</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="12">
         <v>44</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="12">
         <v>22.5</v>
       </c>
       <c r="G70" s="2">
@@ -8373,16 +8394,16 @@
       <c r="B78" s="1">
         <v>179600</v>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="11">
         <v>6150</v>
       </c>
-      <c r="D78" s="12">
+      <c r="D78" s="11">
         <v>4800</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="12">
         <v>34.1</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="12">
         <v>26.6</v>
       </c>
       <c r="G78" s="2">
@@ -8421,19 +8442,19 @@
       <c r="A79">
         <v>1932</v>
       </c>
-      <c r="B79" s="12">
+      <c r="B79" s="11">
         <v>180800</v>
       </c>
-      <c r="C79" s="12">
+      <c r="C79" s="11">
         <v>5300</v>
       </c>
-      <c r="D79" s="12">
+      <c r="D79" s="11">
         <v>4200</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="12">
         <v>29.2</v>
       </c>
-      <c r="F79" s="13">
+      <c r="F79" s="12">
         <v>23.2</v>
       </c>
       <c r="G79" s="2">
@@ -8472,19 +8493,19 @@
       <c r="A80">
         <v>1933</v>
       </c>
-      <c r="B80" s="12">
+      <c r="B80" s="11">
         <v>181800</v>
       </c>
-      <c r="C80" s="12">
+      <c r="C80" s="11">
         <v>5500</v>
       </c>
-      <c r="D80" s="12">
+      <c r="D80" s="11">
         <v>5900</v>
       </c>
-      <c r="E80" s="13">
+      <c r="E80" s="12">
         <v>30.3</v>
       </c>
-      <c r="F80" s="13">
+      <c r="F80" s="12">
         <v>32.5</v>
       </c>
       <c r="G80" s="2">
@@ -8523,19 +8544,19 @@
       <c r="A81">
         <v>1934</v>
       </c>
-      <c r="B81" s="12">
+      <c r="B81" s="11">
         <v>181300</v>
       </c>
-      <c r="C81" s="12">
+      <c r="C81" s="11">
         <v>4500</v>
       </c>
-      <c r="D81" s="12">
+      <c r="D81" s="11">
         <v>6200</v>
       </c>
-      <c r="E81" s="13">
+      <c r="E81" s="12">
         <v>25</v>
       </c>
-      <c r="F81" s="13">
+      <c r="F81" s="12">
         <v>34.4</v>
       </c>
       <c r="G81" s="2">
@@ -8781,16 +8802,16 @@
       <c r="B86" s="1">
         <v>191400</v>
       </c>
-      <c r="C86" s="12">
+      <c r="C86" s="11">
         <v>6400</v>
       </c>
-      <c r="D86" s="12">
+      <c r="D86" s="11">
         <v>4450</v>
       </c>
-      <c r="E86" s="13">
+      <c r="E86" s="12">
         <v>33.299999999999997</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F86" s="12">
         <v>23.2</v>
       </c>
       <c r="G86" s="2">
@@ -8883,16 +8904,16 @@
       <c r="B88" s="1">
         <v>195000</v>
       </c>
-      <c r="C88" s="12">
+      <c r="C88" s="11">
         <v>6120</v>
       </c>
-      <c r="D88" s="12">
+      <c r="D88" s="11">
         <v>7050</v>
       </c>
-      <c r="E88" s="13">
+      <c r="E88" s="12">
         <v>31.5</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="12">
         <v>36.299999999999997</v>
       </c>
       <c r="G88" s="2">
@@ -8931,19 +8952,19 @@
       <c r="A89">
         <v>1942</v>
       </c>
-      <c r="B89" s="12">
+      <c r="B89" s="11">
         <v>193800</v>
       </c>
-      <c r="C89" s="12">
+      <c r="C89" s="11">
         <v>4750</v>
       </c>
-      <c r="D89" s="12">
+      <c r="D89" s="11">
         <v>10200</v>
       </c>
-      <c r="E89" s="13">
+      <c r="E89" s="12">
         <v>24.9</v>
       </c>
-      <c r="F89" s="13">
+      <c r="F89" s="12">
         <v>53.4</v>
       </c>
       <c r="G89" s="2">
@@ -8982,19 +9003,19 @@
       <c r="A90">
         <v>1943</v>
       </c>
-      <c r="B90" s="12">
+      <c r="B90" s="11">
         <v>188100</v>
       </c>
-      <c r="C90" s="12">
+      <c r="C90" s="11">
         <v>3800</v>
       </c>
-      <c r="D90" s="12">
+      <c r="D90" s="11">
         <v>9300</v>
       </c>
-      <c r="E90" s="13">
+      <c r="E90" s="12">
         <v>20.5</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90" s="12">
         <v>50.2</v>
       </c>
       <c r="G90" s="2">
@@ -9033,19 +9054,19 @@
       <c r="A91">
         <v>1944</v>
       </c>
-      <c r="B91" s="12">
+      <c r="B91" s="11">
         <v>182500</v>
       </c>
-      <c r="C91" s="12">
+      <c r="C91" s="11">
         <v>3100</v>
       </c>
-      <c r="D91" s="12">
+      <c r="D91" s="11">
         <v>8200</v>
       </c>
-      <c r="E91" s="13">
+      <c r="E91" s="12">
         <v>17.2</v>
       </c>
-      <c r="F91" s="13">
+      <c r="F91" s="12">
         <v>45.6</v>
       </c>
       <c r="G91" s="2">
@@ -9084,19 +9105,19 @@
       <c r="A92">
         <v>1945</v>
       </c>
-      <c r="B92" s="12">
+      <c r="B92" s="11">
         <v>177300</v>
       </c>
-      <c r="C92" s="12">
+      <c r="C92" s="11">
         <v>2800</v>
       </c>
-      <c r="D92" s="12">
+      <c r="D92" s="11">
         <v>5800</v>
       </c>
-      <c r="E92" s="13">
+      <c r="E92" s="12">
         <v>15.9</v>
       </c>
-      <c r="F92" s="13">
+      <c r="F92" s="12">
         <v>33</v>
       </c>
       <c r="G92" s="2">
@@ -9135,19 +9156,19 @@
       <c r="A93">
         <v>1946</v>
       </c>
-      <c r="B93" s="12">
+      <c r="B93" s="11">
         <v>174000</v>
       </c>
-      <c r="C93" s="12">
+      <c r="C93" s="11">
         <v>4550</v>
       </c>
-      <c r="D93" s="12">
+      <c r="D93" s="11">
         <v>3950</v>
       </c>
-      <c r="E93" s="13">
+      <c r="E93" s="12">
         <v>26.2</v>
       </c>
-      <c r="F93" s="13">
+      <c r="F93" s="12">
         <v>22.7</v>
       </c>
       <c r="G93" s="2">
@@ -9186,16 +9207,16 @@
       <c r="A94">
         <v>1947</v>
       </c>
-      <c r="B94" s="12">
+      <c r="B94" s="11">
         <v>173600</v>
       </c>
-      <c r="C94" s="12">
+      <c r="C94" s="11">
         <v>5220</v>
       </c>
       <c r="D94" s="1">
         <v>3770</v>
       </c>
-      <c r="E94" s="13">
+      <c r="E94" s="12">
         <v>29.9</v>
       </c>
       <c r="F94" s="2">
@@ -9237,16 +9258,16 @@
       <c r="A95">
         <v>1948</v>
       </c>
-      <c r="B95" s="12">
+      <c r="B95" s="11">
         <v>175100</v>
       </c>
-      <c r="C95" s="12">
+      <c r="C95" s="11">
         <v>5060</v>
       </c>
       <c r="D95" s="1">
         <v>2790</v>
       </c>
-      <c r="E95" s="13">
+      <c r="E95" s="12">
         <v>28.7</v>
       </c>
       <c r="F95" s="2">
@@ -9288,19 +9309,19 @@
       <c r="A96">
         <v>1949</v>
       </c>
-      <c r="B96" s="12">
+      <c r="B96" s="11">
         <v>177300</v>
       </c>
-      <c r="C96" s="12">
+      <c r="C96" s="11">
         <v>5010</v>
       </c>
-      <c r="D96" s="12">
+      <c r="D96" s="11">
         <v>2440</v>
       </c>
-      <c r="E96" s="13">
+      <c r="E96" s="12">
         <v>28</v>
       </c>
-      <c r="F96" s="13">
+      <c r="F96" s="12">
         <v>13.7</v>
       </c>
       <c r="I96" s="1">
@@ -9696,24 +9717,24 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>49</v>
       </c>
     </row>
@@ -13121,7 +13142,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>34</v>
       </c>
     </row>

--- a/population-projection/src/main/resources/population_data/Biraben-USSR.xlsx
+++ b/population-projection/src/main/resources/population_data/Biraben-USSR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\population_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D33C1908-BA2F-4947-AC66-D94C056BD916}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A339A8F-1F95-4E72-8628-26B429E02E7A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="3" xr2:uid="{1C2A8E74-6A01-4ECA-AF22-4D7875460B7A}"/>
   </bookViews>
@@ -135,9 +135,6 @@
     <t>среднее</t>
   </si>
   <si>
-    <t>минимум колебаний</t>
-  </si>
-  <si>
     <t>Поведение рождаемости населения территории СССР-1991 по реконструкции Бирабена</t>
   </si>
   <si>
@@ -217,6 +214,9 @@
   </si>
   <si>
     <t>Оцениваемое население не включает не включает прежнее (до 1945 года) немецкое население Калининградской области и японское население Сахалина и Курил,</t>
+  </si>
+  <si>
+    <t>минимум обычных колебаний</t>
   </si>
 </sst>
 </file>
@@ -1709,7 +1709,14 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
-              <a:t>Поведение рождаемости в 1861-1914 годах (Бирабен)</a:t>
+              <a:t>Поведение рождаемости населения территории в границах СССР-1991</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="ru-RU"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>в 1861-1914 годах (Бирабен)</a:t>
             </a:r>
             <a:endParaRPr lang="de-DE"/>
           </a:p>
@@ -2341,166 +2348,166 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="54"/>
                 <c:pt idx="0">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>47.677499999999995</c:v>
+                  <c:v>47.910810810810815</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2521,7 +2528,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>минимум колебаний</c:v>
+                  <c:v>минимум обычных колебаний</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4597,14 +4604,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4624,12 +4631,12 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -4699,7 +4706,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -4709,79 +4716,79 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +4806,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -9718,24 +9725,24 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -13143,7 +13150,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -13157,7 +13164,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -13168,8 +13175,8 @@
         <v>48.8</v>
       </c>
       <c r="C4" s="2">
-        <f>AVERAGE(B4:B43)</f>
-        <v>47.677499999999995</v>
+        <f>AVERAGE(B4:B8,B10:B20,B22:B34,B36:B43)</f>
+        <v>47.910810810810815</v>
       </c>
       <c r="D4" s="2">
         <f>MIN(B4:B8,B10:B20,B22:B34,B36:B43)</f>
@@ -13185,7 +13192,7 @@
       </c>
       <c r="C5" s="2">
         <f>C4</f>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D5" s="2">
         <f>D4</f>
@@ -13201,7 +13208,7 @@
       </c>
       <c r="C6" s="2">
         <f t="shared" ref="C6:C57" si="0">C5</f>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" ref="D6:D57" si="1">D5</f>
@@ -13217,7 +13224,7 @@
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="1"/>
@@ -13233,7 +13240,7 @@
       </c>
       <c r="C8" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="1"/>
@@ -13249,7 +13256,7 @@
       </c>
       <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="1"/>
@@ -13265,7 +13272,7 @@
       </c>
       <c r="C10" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="1"/>
@@ -13281,7 +13288,7 @@
       </c>
       <c r="C11" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D11" s="2">
         <f t="shared" si="1"/>
@@ -13297,7 +13304,7 @@
       </c>
       <c r="C12" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="1"/>
@@ -13313,7 +13320,7 @@
       </c>
       <c r="C13" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D13" s="2">
         <f t="shared" si="1"/>
@@ -13329,7 +13336,7 @@
       </c>
       <c r="C14" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="1"/>
@@ -13345,7 +13352,7 @@
       </c>
       <c r="C15" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D15" s="2">
         <f t="shared" si="1"/>
@@ -13361,7 +13368,7 @@
       </c>
       <c r="C16" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="1"/>
@@ -13377,7 +13384,7 @@
       </c>
       <c r="C17" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D17" s="2">
         <f t="shared" si="1"/>
@@ -13393,7 +13400,7 @@
       </c>
       <c r="C18" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D18" s="2">
         <f t="shared" si="1"/>
@@ -13409,7 +13416,7 @@
       </c>
       <c r="C19" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D19" s="2">
         <f t="shared" si="1"/>
@@ -13425,7 +13432,7 @@
       </c>
       <c r="C20" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D20" s="2">
         <f t="shared" si="1"/>
@@ -13441,7 +13448,7 @@
       </c>
       <c r="C21" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D21" s="2">
         <f t="shared" si="1"/>
@@ -13457,7 +13464,7 @@
       </c>
       <c r="C22" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D22" s="2">
         <f t="shared" si="1"/>
@@ -13473,7 +13480,7 @@
       </c>
       <c r="C23" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D23" s="2">
         <f t="shared" si="1"/>
@@ -13489,7 +13496,7 @@
       </c>
       <c r="C24" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D24" s="2">
         <f t="shared" si="1"/>
@@ -13505,7 +13512,7 @@
       </c>
       <c r="C25" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="1"/>
@@ -13521,7 +13528,7 @@
       </c>
       <c r="C26" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="1"/>
@@ -13537,7 +13544,7 @@
       </c>
       <c r="C27" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="1"/>
@@ -13553,7 +13560,7 @@
       </c>
       <c r="C28" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D28" s="2">
         <f t="shared" si="1"/>
@@ -13569,7 +13576,7 @@
       </c>
       <c r="C29" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" si="1"/>
@@ -13585,7 +13592,7 @@
       </c>
       <c r="C30" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="1"/>
@@ -13601,7 +13608,7 @@
       </c>
       <c r="C31" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D31" s="2">
         <f t="shared" si="1"/>
@@ -13617,7 +13624,7 @@
       </c>
       <c r="C32" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D32" s="2">
         <f t="shared" si="1"/>
@@ -13633,7 +13640,7 @@
       </c>
       <c r="C33" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D33" s="2">
         <f t="shared" si="1"/>
@@ -13649,7 +13656,7 @@
       </c>
       <c r="C34" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D34" s="2">
         <f t="shared" si="1"/>
@@ -13665,7 +13672,7 @@
       </c>
       <c r="C35" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D35" s="2">
         <f t="shared" si="1"/>
@@ -13681,7 +13688,7 @@
       </c>
       <c r="C36" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D36" s="2">
         <f t="shared" si="1"/>
@@ -13697,7 +13704,7 @@
       </c>
       <c r="C37" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D37" s="2">
         <f t="shared" si="1"/>
@@ -13713,7 +13720,7 @@
       </c>
       <c r="C38" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D38" s="2">
         <f t="shared" si="1"/>
@@ -13729,7 +13736,7 @@
       </c>
       <c r="C39" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D39" s="2">
         <f t="shared" si="1"/>
@@ -13745,7 +13752,7 @@
       </c>
       <c r="C40" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D40" s="2">
         <f t="shared" si="1"/>
@@ -13761,7 +13768,7 @@
       </c>
       <c r="C41" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D41" s="2">
         <f t="shared" si="1"/>
@@ -13777,7 +13784,7 @@
       </c>
       <c r="C42" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D42" s="2">
         <f t="shared" si="1"/>
@@ -13793,7 +13800,7 @@
       </c>
       <c r="C43" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D43" s="2">
         <f t="shared" si="1"/>
@@ -13809,7 +13816,7 @@
       </c>
       <c r="C44" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D44" s="2">
         <f t="shared" si="1"/>
@@ -13825,7 +13832,7 @@
       </c>
       <c r="C45" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D45" s="2">
         <f t="shared" si="1"/>
@@ -13841,7 +13848,7 @@
       </c>
       <c r="C46" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D46" s="2">
         <f t="shared" si="1"/>
@@ -13857,7 +13864,7 @@
       </c>
       <c r="C47" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D47" s="2">
         <f t="shared" si="1"/>
@@ -13873,7 +13880,7 @@
       </c>
       <c r="C48" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D48" s="2">
         <f t="shared" si="1"/>
@@ -13889,7 +13896,7 @@
       </c>
       <c r="C49" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D49" s="2">
         <f t="shared" si="1"/>
@@ -13905,7 +13912,7 @@
       </c>
       <c r="C50" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D50" s="2">
         <f t="shared" si="1"/>
@@ -13921,7 +13928,7 @@
       </c>
       <c r="C51" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D51" s="2">
         <f t="shared" si="1"/>
@@ -13937,7 +13944,7 @@
       </c>
       <c r="C52" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D52" s="2">
         <f t="shared" si="1"/>
@@ -13953,7 +13960,7 @@
       </c>
       <c r="C53" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D53" s="2">
         <f t="shared" si="1"/>
@@ -13969,7 +13976,7 @@
       </c>
       <c r="C54" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D54" s="2">
         <f t="shared" si="1"/>
@@ -13985,7 +13992,7 @@
       </c>
       <c r="C55" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D55" s="2">
         <f t="shared" si="1"/>
@@ -14001,7 +14008,7 @@
       </c>
       <c r="C56" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D56" s="2">
         <f t="shared" si="1"/>
@@ -14017,7 +14024,7 @@
       </c>
       <c r="C57" s="2">
         <f t="shared" si="0"/>
-        <v>47.677499999999995</v>
+        <v>47.910810810810815</v>
       </c>
       <c r="D57" s="2">
         <f t="shared" si="1"/>
